--- a/output/pdf_financials_xlsx/YAY.xlsx
+++ b/output/pdf_financials_xlsx/YAY.xlsx
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.036109</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.116321</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>2.683597</v>
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.036109</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.116321</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.844777</v>
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001492</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012002</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1026,10 +1026,10 @@
         <v>-0.036109</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.114829</v>
+        <v>-0.116321</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.666139</v>
+        <v>-2.678141</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.998943</v>
@@ -1070,10 +1070,10 @@
         <v>-0.036109</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.114829</v>
+        <v>-0.116321</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.666139</v>
+        <v>-2.678141</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.998943</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-25.86463759817936</v>
+        <v>-25.98107090508998</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-51.63432013749212</v>
@@ -1176,13 +1176,13 @@
         <v>0.71001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.700583</v>
+        <v>0.08068699999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.0163</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.07978200000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1220,13 +1220,13 @@
         <v>0.71001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.700583</v>
+        <v>0.08068699999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.0163</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.07978200000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1484,13 +1484,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0</v>
+        <v>0.08910899999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.188126</v>
+        <v>0.171826</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.295984</v>
+        <v>0.216202</v>
       </c>
     </row>
     <row r="49">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">

--- a/output/pdf_financials_xlsx/YAY.xlsx
+++ b/output/pdf_financials_xlsx/YAY.xlsx
@@ -1051,13 +1051,13 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.311723</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.173802</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.398126</v>
       </c>
     </row>
     <row r="29">
@@ -1073,13 +1073,13 @@
         <v>-0.116321</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.678141</v>
+        <v>-2.366418</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.998943</v>
+        <v>-2.825141</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.547504</v>
+        <v>-1.149378</v>
       </c>
     </row>
     <row r="30">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-25.98107090508998</v>
+        <v>-22.95699660663169</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-51.63432013749212</v>
+        <v>-48.6418830993302</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-10.71824301889218</v>
+        <v>-7.960763089832566</v>
       </c>
     </row>
     <row r="31">
@@ -2641,13 +2641,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.311723</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.173802</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.398126</v>
       </c>
     </row>
     <row r="101">
@@ -5708,7 +5708,11 @@
           <t>Depreciation of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -5782,7 +5786,11 @@
           <t>Depreciation of right-of-use assets (Note 12)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/YAY.xlsx
+++ b/output/pdf_financials_xlsx/YAY.xlsx
@@ -6711,7 +6711,11 @@
           <t>Proceeds of private placement (Note 4)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -7494,7 +7498,11 @@
           <t>Proceeds of private placement (Note 4)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -8113,7 +8121,11 @@
           <t>Proceeds from share issuance 6</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -8537,7 +8549,11 @@
           <t>Proceeds from share issuance 6 $</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="n">
         <v>0.6</v>
       </c>
